--- a/giro_da_praça_ofertas - sexta.xlsx
+++ b/giro_da_praça_ofertas - sexta.xlsx
@@ -476,14 +476,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -807,234 +807,6 @@
         <v>18.99</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>261696</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>COXA DE FRANGO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>TEMPERADA</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>108785</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>108856</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>108786</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>FILEZINHO DE PEITO DE FRANGO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="n">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>109388</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>FRANGO A PASSARINHO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
-        <v>16.99</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>195365</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #01 AVES</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>104601</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>289127</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
-        <v>8.49</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>SEXTA/DOMINGO - 12 A 14/12/25</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>320120</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>LINGUIÇA SUINA MIMOSA KG APIMENTADA</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
